--- a/public/deviceExcel/sensor.xlsx
+++ b/public/deviceExcel/sensor.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\energy设备导入文件\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chint-react\ses\public\deviceExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,10 +27,6 @@
     <t>告警方案</t>
   </si>
   <si>
-    <t>*客户类别(客户用能/公用用能)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>*所属区域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -64,6 +60,10 @@
   </si>
   <si>
     <t>*传感器型号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*客户类别(客户用能/公共用能)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,22 +430,22 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -454,16 +454,16 @@
         <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/public/deviceExcel/sensor.xlsx
+++ b/public/deviceExcel/sensor.xlsx
@@ -35,35 +35,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>通讯协议（Modbus/DL645）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*传感器名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*传感器型号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>通讯地址(0,255)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>通讯协议（Modbus/DL645）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*通讯端口[1,16]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*网关编号（*为必填项）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*传感器编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*传感器名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*传感器型号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*客户类别(客户用能/公共用能)</t>
+    <t>通讯端口[1,16]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网关编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*传感器编号（*为必填项）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户类别(客户/公共)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,16 +430,16 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -454,13 +454,13 @@
         <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>3</v>
